--- a/etf_holdings/2026-10-19_daily_changes_changed_only.xlsx
+++ b/etf_holdings/2026-10-19_daily_changes_changed_only.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M360"/>
+  <dimension ref="A1:M398"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -16908,6 +16908,1716 @@
         </is>
       </c>
     </row>
+    <row r="361">
+      <c r="A361" t="inlineStr">
+        <is>
+          <t>00400A</t>
+        </is>
+      </c>
+      <c r="B361" t="inlineStr">
+        <is>
+          <t>新增</t>
+        </is>
+      </c>
+      <c r="C361" t="inlineStr">
+        <is>
+          <t>新納入</t>
+        </is>
+      </c>
+      <c r="D361" t="inlineStr">
+        <is>
+          <t>1215</t>
+        </is>
+      </c>
+      <c r="E361" t="inlineStr"/>
+      <c r="F361" t="inlineStr">
+        <is>
+          <t>卜蜂</t>
+        </is>
+      </c>
+      <c r="G361" t="inlineStr"/>
+      <c r="H361" t="inlineStr">
+        <is>
+          <t>0.07%</t>
+        </is>
+      </c>
+      <c r="I361" t="inlineStr"/>
+      <c r="J361" t="inlineStr"/>
+      <c r="K361" t="n">
+        <v>200000</v>
+      </c>
+      <c r="L361" t="inlineStr"/>
+      <c r="M361" t="inlineStr">
+        <is>
+          <t>2026-10-18_00400A_full_holdings.xlsx</t>
+        </is>
+      </c>
+    </row>
+    <row r="362">
+      <c r="A362" t="inlineStr">
+        <is>
+          <t>00400A</t>
+        </is>
+      </c>
+      <c r="B362" t="inlineStr">
+        <is>
+          <t>新增</t>
+        </is>
+      </c>
+      <c r="C362" t="inlineStr">
+        <is>
+          <t>新納入</t>
+        </is>
+      </c>
+      <c r="D362" t="inlineStr">
+        <is>
+          <t>1476</t>
+        </is>
+      </c>
+      <c r="E362" t="inlineStr"/>
+      <c r="F362" t="inlineStr">
+        <is>
+          <t>儒鴻</t>
+        </is>
+      </c>
+      <c r="G362" t="inlineStr"/>
+      <c r="H362" t="inlineStr">
+        <is>
+          <t>0.07%</t>
+        </is>
+      </c>
+      <c r="I362" t="inlineStr"/>
+      <c r="J362" t="inlineStr"/>
+      <c r="K362" t="n">
+        <v>70000</v>
+      </c>
+      <c r="L362" t="inlineStr"/>
+      <c r="M362" t="inlineStr">
+        <is>
+          <t>2026-10-18_00400A_full_holdings.xlsx</t>
+        </is>
+      </c>
+    </row>
+    <row r="363">
+      <c r="A363" t="inlineStr">
+        <is>
+          <t>00400A</t>
+        </is>
+      </c>
+      <c r="B363" t="inlineStr">
+        <is>
+          <t>新增</t>
+        </is>
+      </c>
+      <c r="C363" t="inlineStr">
+        <is>
+          <t>新納入</t>
+        </is>
+      </c>
+      <c r="D363" t="inlineStr">
+        <is>
+          <t>2303</t>
+        </is>
+      </c>
+      <c r="E363" t="inlineStr"/>
+      <c r="F363" t="inlineStr">
+        <is>
+          <t>聯電</t>
+        </is>
+      </c>
+      <c r="G363" t="inlineStr"/>
+      <c r="H363" t="inlineStr">
+        <is>
+          <t>1.81%</t>
+        </is>
+      </c>
+      <c r="I363" t="inlineStr"/>
+      <c r="J363" t="inlineStr"/>
+      <c r="K363" t="n">
+        <v>4192000</v>
+      </c>
+      <c r="L363" t="inlineStr"/>
+      <c r="M363" t="inlineStr">
+        <is>
+          <t>2026-10-18_00400A_full_holdings.xlsx</t>
+        </is>
+      </c>
+    </row>
+    <row r="364">
+      <c r="A364" t="inlineStr">
+        <is>
+          <t>00400A</t>
+        </is>
+      </c>
+      <c r="B364" t="inlineStr">
+        <is>
+          <t>新增</t>
+        </is>
+      </c>
+      <c r="C364" t="inlineStr">
+        <is>
+          <t>新納入</t>
+        </is>
+      </c>
+      <c r="D364" t="inlineStr">
+        <is>
+          <t>2313</t>
+        </is>
+      </c>
+      <c r="E364" t="inlineStr"/>
+      <c r="F364" t="inlineStr">
+        <is>
+          <t>華通</t>
+        </is>
+      </c>
+      <c r="G364" t="inlineStr"/>
+      <c r="H364" t="inlineStr">
+        <is>
+          <t>0.90%</t>
+        </is>
+      </c>
+      <c r="I364" t="inlineStr"/>
+      <c r="J364" t="inlineStr"/>
+      <c r="K364" t="n">
+        <v>1107336</v>
+      </c>
+      <c r="L364" t="inlineStr"/>
+      <c r="M364" t="inlineStr">
+        <is>
+          <t>2026-10-18_00400A_full_holdings.xlsx</t>
+        </is>
+      </c>
+    </row>
+    <row r="365">
+      <c r="A365" t="inlineStr">
+        <is>
+          <t>00400A</t>
+        </is>
+      </c>
+      <c r="B365" t="inlineStr">
+        <is>
+          <t>新增</t>
+        </is>
+      </c>
+      <c r="C365" t="inlineStr">
+        <is>
+          <t>新納入</t>
+        </is>
+      </c>
+      <c r="D365" t="inlineStr">
+        <is>
+          <t>2317</t>
+        </is>
+      </c>
+      <c r="E365" t="inlineStr"/>
+      <c r="F365" t="inlineStr">
+        <is>
+          <t>鴻海</t>
+        </is>
+      </c>
+      <c r="G365" t="inlineStr"/>
+      <c r="H365" t="inlineStr">
+        <is>
+          <t>0.76%</t>
+        </is>
+      </c>
+      <c r="I365" t="inlineStr"/>
+      <c r="J365" t="inlineStr"/>
+      <c r="K365" t="n">
+        <v>960000</v>
+      </c>
+      <c r="L365" t="inlineStr"/>
+      <c r="M365" t="inlineStr">
+        <is>
+          <t>2026-10-18_00400A_full_holdings.xlsx</t>
+        </is>
+      </c>
+    </row>
+    <row r="366">
+      <c r="A366" t="inlineStr">
+        <is>
+          <t>00400A</t>
+        </is>
+      </c>
+      <c r="B366" t="inlineStr">
+        <is>
+          <t>新增</t>
+        </is>
+      </c>
+      <c r="C366" t="inlineStr">
+        <is>
+          <t>新納入</t>
+        </is>
+      </c>
+      <c r="D366" t="inlineStr">
+        <is>
+          <t>2327</t>
+        </is>
+      </c>
+      <c r="E366" t="inlineStr"/>
+      <c r="F366" t="inlineStr">
+        <is>
+          <t>國巨*</t>
+        </is>
+      </c>
+      <c r="G366" t="inlineStr"/>
+      <c r="H366" t="inlineStr">
+        <is>
+          <t>1.24%</t>
+        </is>
+      </c>
+      <c r="I366" t="inlineStr"/>
+      <c r="J366" t="inlineStr"/>
+      <c r="K366" t="n">
+        <v>708000</v>
+      </c>
+      <c r="L366" t="inlineStr"/>
+      <c r="M366" t="inlineStr">
+        <is>
+          <t>2026-10-18_00400A_full_holdings.xlsx</t>
+        </is>
+      </c>
+    </row>
+    <row r="367">
+      <c r="A367" t="inlineStr">
+        <is>
+          <t>00400A</t>
+        </is>
+      </c>
+      <c r="B367" t="inlineStr">
+        <is>
+          <t>新增</t>
+        </is>
+      </c>
+      <c r="C367" t="inlineStr">
+        <is>
+          <t>新納入</t>
+        </is>
+      </c>
+      <c r="D367" t="inlineStr">
+        <is>
+          <t>2345</t>
+        </is>
+      </c>
+      <c r="E367" t="inlineStr"/>
+      <c r="F367" t="inlineStr">
+        <is>
+          <t>智邦</t>
+        </is>
+      </c>
+      <c r="G367" t="inlineStr"/>
+      <c r="H367" t="inlineStr">
+        <is>
+          <t>0.69%</t>
+        </is>
+      </c>
+      <c r="I367" t="inlineStr"/>
+      <c r="J367" t="inlineStr"/>
+      <c r="K367" t="n">
+        <v>104000</v>
+      </c>
+      <c r="L367" t="inlineStr"/>
+      <c r="M367" t="inlineStr">
+        <is>
+          <t>2026-10-18_00400A_full_holdings.xlsx</t>
+        </is>
+      </c>
+    </row>
+    <row r="368">
+      <c r="A368" t="inlineStr">
+        <is>
+          <t>00400A</t>
+        </is>
+      </c>
+      <c r="B368" t="inlineStr">
+        <is>
+          <t>新增</t>
+        </is>
+      </c>
+      <c r="C368" t="inlineStr">
+        <is>
+          <t>新納入</t>
+        </is>
+      </c>
+      <c r="D368" t="inlineStr">
+        <is>
+          <t>2449</t>
+        </is>
+      </c>
+      <c r="E368" t="inlineStr"/>
+      <c r="F368" t="inlineStr">
+        <is>
+          <t>京元電子</t>
+        </is>
+      </c>
+      <c r="G368" t="inlineStr"/>
+      <c r="H368" t="inlineStr">
+        <is>
+          <t>0.87%</t>
+        </is>
+      </c>
+      <c r="I368" t="inlineStr"/>
+      <c r="J368" t="inlineStr"/>
+      <c r="K368" t="n">
+        <v>999000</v>
+      </c>
+      <c r="L368" t="inlineStr"/>
+      <c r="M368" t="inlineStr">
+        <is>
+          <t>2026-10-18_00400A_full_holdings.xlsx</t>
+        </is>
+      </c>
+    </row>
+    <row r="369">
+      <c r="A369" t="inlineStr">
+        <is>
+          <t>00400A</t>
+        </is>
+      </c>
+      <c r="B369" t="inlineStr">
+        <is>
+          <t>新增</t>
+        </is>
+      </c>
+      <c r="C369" t="inlineStr">
+        <is>
+          <t>新納入</t>
+        </is>
+      </c>
+      <c r="D369" t="inlineStr">
+        <is>
+          <t>2603</t>
+        </is>
+      </c>
+      <c r="E369" t="inlineStr"/>
+      <c r="F369" t="inlineStr">
+        <is>
+          <t>長榮</t>
+        </is>
+      </c>
+      <c r="G369" t="inlineStr"/>
+      <c r="H369" t="inlineStr">
+        <is>
+          <t>1.61%</t>
+        </is>
+      </c>
+      <c r="I369" t="inlineStr"/>
+      <c r="J369" t="inlineStr"/>
+      <c r="K369" t="n">
+        <v>1871000</v>
+      </c>
+      <c r="L369" t="inlineStr"/>
+      <c r="M369" t="inlineStr">
+        <is>
+          <t>2026-10-18_00400A_full_holdings.xlsx</t>
+        </is>
+      </c>
+    </row>
+    <row r="370">
+      <c r="A370" t="inlineStr">
+        <is>
+          <t>00400A</t>
+        </is>
+      </c>
+      <c r="B370" t="inlineStr">
+        <is>
+          <t>新增</t>
+        </is>
+      </c>
+      <c r="C370" t="inlineStr">
+        <is>
+          <t>新納入</t>
+        </is>
+      </c>
+      <c r="D370" t="inlineStr">
+        <is>
+          <t>2637</t>
+        </is>
+      </c>
+      <c r="E370" t="inlineStr"/>
+      <c r="F370" t="inlineStr">
+        <is>
+          <t>慧洋-KY</t>
+        </is>
+      </c>
+      <c r="G370" t="inlineStr"/>
+      <c r="H370" t="inlineStr">
+        <is>
+          <t>0.47%</t>
+        </is>
+      </c>
+      <c r="I370" t="inlineStr"/>
+      <c r="J370" t="inlineStr"/>
+      <c r="K370" t="n">
+        <v>1424000</v>
+      </c>
+      <c r="L370" t="inlineStr"/>
+      <c r="M370" t="inlineStr">
+        <is>
+          <t>2026-10-18_00400A_full_holdings.xlsx</t>
+        </is>
+      </c>
+    </row>
+    <row r="371">
+      <c r="A371" t="inlineStr">
+        <is>
+          <t>00400A</t>
+        </is>
+      </c>
+      <c r="B371" t="inlineStr">
+        <is>
+          <t>新增</t>
+        </is>
+      </c>
+      <c r="C371" t="inlineStr">
+        <is>
+          <t>新納入</t>
+        </is>
+      </c>
+      <c r="D371" t="inlineStr">
+        <is>
+          <t>2881</t>
+        </is>
+      </c>
+      <c r="E371" t="inlineStr"/>
+      <c r="F371" t="inlineStr">
+        <is>
+          <t>富邦金</t>
+        </is>
+      </c>
+      <c r="G371" t="inlineStr"/>
+      <c r="H371" t="inlineStr">
+        <is>
+          <t>1.62%</t>
+        </is>
+      </c>
+      <c r="I371" t="inlineStr"/>
+      <c r="J371" t="inlineStr"/>
+      <c r="K371" t="n">
+        <v>3104000</v>
+      </c>
+      <c r="L371" t="inlineStr"/>
+      <c r="M371" t="inlineStr">
+        <is>
+          <t>2026-10-18_00400A_full_holdings.xlsx</t>
+        </is>
+      </c>
+    </row>
+    <row r="372">
+      <c r="A372" t="inlineStr">
+        <is>
+          <t>00400A</t>
+        </is>
+      </c>
+      <c r="B372" t="inlineStr">
+        <is>
+          <t>新增</t>
+        </is>
+      </c>
+      <c r="C372" t="inlineStr">
+        <is>
+          <t>新納入</t>
+        </is>
+      </c>
+      <c r="D372" t="inlineStr">
+        <is>
+          <t>2891</t>
+        </is>
+      </c>
+      <c r="E372" t="inlineStr"/>
+      <c r="F372" t="inlineStr">
+        <is>
+          <t>中信金</t>
+        </is>
+      </c>
+      <c r="G372" t="inlineStr"/>
+      <c r="H372" t="inlineStr">
+        <is>
+          <t>1.58%</t>
+        </is>
+      </c>
+      <c r="I372" t="inlineStr"/>
+      <c r="J372" t="inlineStr"/>
+      <c r="K372" t="n">
+        <v>6547000</v>
+      </c>
+      <c r="L372" t="inlineStr"/>
+      <c r="M372" t="inlineStr">
+        <is>
+          <t>2026-10-18_00400A_full_holdings.xlsx</t>
+        </is>
+      </c>
+    </row>
+    <row r="373">
+      <c r="A373" t="inlineStr">
+        <is>
+          <t>00400A</t>
+        </is>
+      </c>
+      <c r="B373" t="inlineStr">
+        <is>
+          <t>新增</t>
+        </is>
+      </c>
+      <c r="C373" t="inlineStr">
+        <is>
+          <t>新納入</t>
+        </is>
+      </c>
+      <c r="D373" t="inlineStr">
+        <is>
+          <t>3008</t>
+        </is>
+      </c>
+      <c r="E373" t="inlineStr"/>
+      <c r="F373" t="inlineStr">
+        <is>
+          <t>大立光</t>
+        </is>
+      </c>
+      <c r="G373" t="inlineStr"/>
+      <c r="H373" t="inlineStr">
+        <is>
+          <t>1.56%</t>
+        </is>
+      </c>
+      <c r="I373" t="inlineStr"/>
+      <c r="J373" t="inlineStr"/>
+      <c r="K373" t="n">
+        <v>76000</v>
+      </c>
+      <c r="L373" t="inlineStr"/>
+      <c r="M373" t="inlineStr">
+        <is>
+          <t>2026-10-18_00400A_full_holdings.xlsx</t>
+        </is>
+      </c>
+    </row>
+    <row r="374">
+      <c r="A374" t="inlineStr">
+        <is>
+          <t>00400A</t>
+        </is>
+      </c>
+      <c r="B374" t="inlineStr">
+        <is>
+          <t>新增</t>
+        </is>
+      </c>
+      <c r="C374" t="inlineStr">
+        <is>
+          <t>新納入</t>
+        </is>
+      </c>
+      <c r="D374" t="inlineStr">
+        <is>
+          <t>3036</t>
+        </is>
+      </c>
+      <c r="E374" t="inlineStr"/>
+      <c r="F374" t="inlineStr">
+        <is>
+          <t>文曄</t>
+        </is>
+      </c>
+      <c r="G374" t="inlineStr"/>
+      <c r="H374" t="inlineStr">
+        <is>
+          <t>1.49%</t>
+        </is>
+      </c>
+      <c r="I374" t="inlineStr"/>
+      <c r="J374" t="inlineStr"/>
+      <c r="K374" t="n">
+        <v>2208000</v>
+      </c>
+      <c r="L374" t="inlineStr"/>
+      <c r="M374" t="inlineStr">
+        <is>
+          <t>2026-10-18_00400A_full_holdings.xlsx</t>
+        </is>
+      </c>
+    </row>
+    <row r="375">
+      <c r="A375" t="inlineStr">
+        <is>
+          <t>00400A</t>
+        </is>
+      </c>
+      <c r="B375" t="inlineStr">
+        <is>
+          <t>新增</t>
+        </is>
+      </c>
+      <c r="C375" t="inlineStr">
+        <is>
+          <t>新納入</t>
+        </is>
+      </c>
+      <c r="D375" t="inlineStr">
+        <is>
+          <t>3081</t>
+        </is>
+      </c>
+      <c r="E375" t="inlineStr"/>
+      <c r="F375" t="inlineStr">
+        <is>
+          <t>聯亞</t>
+        </is>
+      </c>
+      <c r="G375" t="inlineStr"/>
+      <c r="H375" t="inlineStr">
+        <is>
+          <t>0.69%</t>
+        </is>
+      </c>
+      <c r="I375" t="inlineStr"/>
+      <c r="J375" t="inlineStr"/>
+      <c r="K375" t="n">
+        <v>82000</v>
+      </c>
+      <c r="L375" t="inlineStr"/>
+      <c r="M375" t="inlineStr">
+        <is>
+          <t>2026-10-18_00400A_full_holdings.xlsx</t>
+        </is>
+      </c>
+    </row>
+    <row r="376">
+      <c r="A376" t="inlineStr">
+        <is>
+          <t>00400A</t>
+        </is>
+      </c>
+      <c r="B376" t="inlineStr">
+        <is>
+          <t>新增</t>
+        </is>
+      </c>
+      <c r="C376" t="inlineStr">
+        <is>
+          <t>新納入</t>
+        </is>
+      </c>
+      <c r="D376" t="inlineStr">
+        <is>
+          <t>3090</t>
+        </is>
+      </c>
+      <c r="E376" t="inlineStr"/>
+      <c r="F376" t="inlineStr">
+        <is>
+          <t>日電貿</t>
+        </is>
+      </c>
+      <c r="G376" t="inlineStr"/>
+      <c r="H376" t="inlineStr">
+        <is>
+          <t>0.32%</t>
+        </is>
+      </c>
+      <c r="I376" t="inlineStr"/>
+      <c r="J376" t="inlineStr"/>
+      <c r="K376" t="n">
+        <v>592000</v>
+      </c>
+      <c r="L376" t="inlineStr"/>
+      <c r="M376" t="inlineStr">
+        <is>
+          <t>2026-10-18_00400A_full_holdings.xlsx</t>
+        </is>
+      </c>
+    </row>
+    <row r="377">
+      <c r="A377" t="inlineStr">
+        <is>
+          <t>00400A</t>
+        </is>
+      </c>
+      <c r="B377" t="inlineStr">
+        <is>
+          <t>新增</t>
+        </is>
+      </c>
+      <c r="C377" t="inlineStr">
+        <is>
+          <t>新納入</t>
+        </is>
+      </c>
+      <c r="D377" t="inlineStr">
+        <is>
+          <t>3167</t>
+        </is>
+      </c>
+      <c r="E377" t="inlineStr"/>
+      <c r="F377" t="inlineStr">
+        <is>
+          <t>大量</t>
+        </is>
+      </c>
+      <c r="G377" t="inlineStr"/>
+      <c r="H377" t="inlineStr">
+        <is>
+          <t>0.37%</t>
+        </is>
+      </c>
+      <c r="I377" t="inlineStr"/>
+      <c r="J377" t="inlineStr"/>
+      <c r="K377" t="n">
+        <v>115000</v>
+      </c>
+      <c r="L377" t="inlineStr"/>
+      <c r="M377" t="inlineStr">
+        <is>
+          <t>2026-10-18_00400A_full_holdings.xlsx</t>
+        </is>
+      </c>
+    </row>
+    <row r="378">
+      <c r="A378" t="inlineStr">
+        <is>
+          <t>00400A</t>
+        </is>
+      </c>
+      <c r="B378" t="inlineStr">
+        <is>
+          <t>新增</t>
+        </is>
+      </c>
+      <c r="C378" t="inlineStr">
+        <is>
+          <t>新納入</t>
+        </is>
+      </c>
+      <c r="D378" t="inlineStr">
+        <is>
+          <t>3231</t>
+        </is>
+      </c>
+      <c r="E378" t="inlineStr"/>
+      <c r="F378" t="inlineStr">
+        <is>
+          <t>緯創</t>
+        </is>
+      </c>
+      <c r="G378" t="inlineStr"/>
+      <c r="H378" t="inlineStr">
+        <is>
+          <t>0.96%</t>
+        </is>
+      </c>
+      <c r="I378" t="inlineStr"/>
+      <c r="J378" t="inlineStr"/>
+      <c r="K378" t="n">
+        <v>1614000</v>
+      </c>
+      <c r="L378" t="inlineStr"/>
+      <c r="M378" t="inlineStr">
+        <is>
+          <t>2026-10-18_00400A_full_holdings.xlsx</t>
+        </is>
+      </c>
+    </row>
+    <row r="379">
+      <c r="A379" t="inlineStr">
+        <is>
+          <t>00400A</t>
+        </is>
+      </c>
+      <c r="B379" t="inlineStr">
+        <is>
+          <t>新增</t>
+        </is>
+      </c>
+      <c r="C379" t="inlineStr">
+        <is>
+          <t>新納入</t>
+        </is>
+      </c>
+      <c r="D379" t="inlineStr">
+        <is>
+          <t>3293</t>
+        </is>
+      </c>
+      <c r="E379" t="inlineStr"/>
+      <c r="F379" t="inlineStr">
+        <is>
+          <t>鈊象</t>
+        </is>
+      </c>
+      <c r="G379" t="inlineStr"/>
+      <c r="H379" t="inlineStr">
+        <is>
+          <t>0.34%</t>
+        </is>
+      </c>
+      <c r="I379" t="inlineStr"/>
+      <c r="J379" t="inlineStr"/>
+      <c r="K379" t="n">
+        <v>133000</v>
+      </c>
+      <c r="L379" t="inlineStr"/>
+      <c r="M379" t="inlineStr">
+        <is>
+          <t>2026-10-18_00400A_full_holdings.xlsx</t>
+        </is>
+      </c>
+    </row>
+    <row r="380">
+      <c r="A380" t="inlineStr">
+        <is>
+          <t>00400A</t>
+        </is>
+      </c>
+      <c r="B380" t="inlineStr">
+        <is>
+          <t>新增</t>
+        </is>
+      </c>
+      <c r="C380" t="inlineStr">
+        <is>
+          <t>新納入</t>
+        </is>
+      </c>
+      <c r="D380" t="inlineStr">
+        <is>
+          <t>3374</t>
+        </is>
+      </c>
+      <c r="E380" t="inlineStr"/>
+      <c r="F380" t="inlineStr">
+        <is>
+          <t>精材</t>
+        </is>
+      </c>
+      <c r="G380" t="inlineStr"/>
+      <c r="H380" t="inlineStr">
+        <is>
+          <t>0.14%</t>
+        </is>
+      </c>
+      <c r="I380" t="inlineStr"/>
+      <c r="J380" t="inlineStr"/>
+      <c r="K380" t="n">
+        <v>100000</v>
+      </c>
+      <c r="L380" t="inlineStr"/>
+      <c r="M380" t="inlineStr">
+        <is>
+          <t>2026-10-18_00400A_full_holdings.xlsx</t>
+        </is>
+      </c>
+    </row>
+    <row r="381">
+      <c r="A381" t="inlineStr">
+        <is>
+          <t>00400A</t>
+        </is>
+      </c>
+      <c r="B381" t="inlineStr">
+        <is>
+          <t>新增</t>
+        </is>
+      </c>
+      <c r="C381" t="inlineStr">
+        <is>
+          <t>新納入</t>
+        </is>
+      </c>
+      <c r="D381" t="inlineStr">
+        <is>
+          <t>3443</t>
+        </is>
+      </c>
+      <c r="E381" t="inlineStr"/>
+      <c r="F381" t="inlineStr">
+        <is>
+          <t>創意</t>
+        </is>
+      </c>
+      <c r="G381" t="inlineStr"/>
+      <c r="H381" t="inlineStr">
+        <is>
+          <t>2.50%</t>
+        </is>
+      </c>
+      <c r="I381" t="inlineStr"/>
+      <c r="J381" t="inlineStr"/>
+      <c r="K381" t="n">
+        <v>97000</v>
+      </c>
+      <c r="L381" t="inlineStr"/>
+      <c r="M381" t="inlineStr">
+        <is>
+          <t>2026-10-18_00400A_full_holdings.xlsx</t>
+        </is>
+      </c>
+    </row>
+    <row r="382">
+      <c r="A382" t="inlineStr">
+        <is>
+          <t>00400A</t>
+        </is>
+      </c>
+      <c r="B382" t="inlineStr">
+        <is>
+          <t>新增</t>
+        </is>
+      </c>
+      <c r="C382" t="inlineStr">
+        <is>
+          <t>新納入</t>
+        </is>
+      </c>
+      <c r="D382" t="inlineStr">
+        <is>
+          <t>3529</t>
+        </is>
+      </c>
+      <c r="E382" t="inlineStr"/>
+      <c r="F382" t="inlineStr">
+        <is>
+          <t>力旺</t>
+        </is>
+      </c>
+      <c r="G382" t="inlineStr"/>
+      <c r="H382" t="inlineStr">
+        <is>
+          <t>1.26%</t>
+        </is>
+      </c>
+      <c r="I382" t="inlineStr"/>
+      <c r="J382" t="inlineStr"/>
+      <c r="K382" t="n">
+        <v>142000</v>
+      </c>
+      <c r="L382" t="inlineStr"/>
+      <c r="M382" t="inlineStr">
+        <is>
+          <t>2026-10-18_00400A_full_holdings.xlsx</t>
+        </is>
+      </c>
+    </row>
+    <row r="383">
+      <c r="A383" t="inlineStr">
+        <is>
+          <t>00400A</t>
+        </is>
+      </c>
+      <c r="B383" t="inlineStr">
+        <is>
+          <t>新增</t>
+        </is>
+      </c>
+      <c r="C383" t="inlineStr">
+        <is>
+          <t>新納入</t>
+        </is>
+      </c>
+      <c r="D383" t="inlineStr">
+        <is>
+          <t>3533</t>
+        </is>
+      </c>
+      <c r="E383" t="inlineStr"/>
+      <c r="F383" t="inlineStr">
+        <is>
+          <t>嘉澤</t>
+        </is>
+      </c>
+      <c r="G383" t="inlineStr"/>
+      <c r="H383" t="inlineStr">
+        <is>
+          <t>0.91%</t>
+        </is>
+      </c>
+      <c r="I383" t="inlineStr"/>
+      <c r="J383" t="inlineStr"/>
+      <c r="K383" t="n">
+        <v>152000</v>
+      </c>
+      <c r="L383" t="inlineStr"/>
+      <c r="M383" t="inlineStr">
+        <is>
+          <t>2026-10-18_00400A_full_holdings.xlsx</t>
+        </is>
+      </c>
+    </row>
+    <row r="384">
+      <c r="A384" t="inlineStr">
+        <is>
+          <t>00400A</t>
+        </is>
+      </c>
+      <c r="B384" t="inlineStr">
+        <is>
+          <t>新增</t>
+        </is>
+      </c>
+      <c r="C384" t="inlineStr">
+        <is>
+          <t>新納入</t>
+        </is>
+      </c>
+      <c r="D384" t="inlineStr">
+        <is>
+          <t>3661</t>
+        </is>
+      </c>
+      <c r="E384" t="inlineStr"/>
+      <c r="F384" t="inlineStr">
+        <is>
+          <t>世芯-KY</t>
+        </is>
+      </c>
+      <c r="G384" t="inlineStr"/>
+      <c r="H384" t="inlineStr">
+        <is>
+          <t>2.25%</t>
+        </is>
+      </c>
+      <c r="I384" t="inlineStr"/>
+      <c r="J384" t="inlineStr"/>
+      <c r="K384" t="n">
+        <v>184000</v>
+      </c>
+      <c r="L384" t="inlineStr"/>
+      <c r="M384" t="inlineStr">
+        <is>
+          <t>2026-10-18_00400A_full_holdings.xlsx</t>
+        </is>
+      </c>
+    </row>
+    <row r="385">
+      <c r="A385" t="inlineStr">
+        <is>
+          <t>00400A</t>
+        </is>
+      </c>
+      <c r="B385" t="inlineStr">
+        <is>
+          <t>新增</t>
+        </is>
+      </c>
+      <c r="C385" t="inlineStr">
+        <is>
+          <t>新納入</t>
+        </is>
+      </c>
+      <c r="D385" t="inlineStr">
+        <is>
+          <t>3665</t>
+        </is>
+      </c>
+      <c r="E385" t="inlineStr"/>
+      <c r="F385" t="inlineStr">
+        <is>
+          <t>貿聯-KY</t>
+        </is>
+      </c>
+      <c r="G385" t="inlineStr"/>
+      <c r="H385" t="inlineStr">
+        <is>
+          <t>1.48%</t>
+        </is>
+      </c>
+      <c r="I385" t="inlineStr"/>
+      <c r="J385" t="inlineStr"/>
+      <c r="K385" t="n">
+        <v>228000</v>
+      </c>
+      <c r="L385" t="inlineStr"/>
+      <c r="M385" t="inlineStr">
+        <is>
+          <t>2026-10-18_00400A_full_holdings.xlsx</t>
+        </is>
+      </c>
+    </row>
+    <row r="386">
+      <c r="A386" t="inlineStr">
+        <is>
+          <t>00400A</t>
+        </is>
+      </c>
+      <c r="B386" t="inlineStr">
+        <is>
+          <t>新增</t>
+        </is>
+      </c>
+      <c r="C386" t="inlineStr">
+        <is>
+          <t>新納入</t>
+        </is>
+      </c>
+      <c r="D386" t="inlineStr">
+        <is>
+          <t>3711</t>
+        </is>
+      </c>
+      <c r="E386" t="inlineStr"/>
+      <c r="F386" t="inlineStr">
+        <is>
+          <t>日月光投控</t>
+        </is>
+      </c>
+      <c r="G386" t="inlineStr"/>
+      <c r="H386" t="inlineStr">
+        <is>
+          <t>1.02%</t>
+        </is>
+      </c>
+      <c r="I386" t="inlineStr"/>
+      <c r="J386" t="inlineStr"/>
+      <c r="K386" t="n">
+        <v>464000</v>
+      </c>
+      <c r="L386" t="inlineStr"/>
+      <c r="M386" t="inlineStr">
+        <is>
+          <t>2026-10-18_00400A_full_holdings.xlsx</t>
+        </is>
+      </c>
+    </row>
+    <row r="387">
+      <c r="A387" t="inlineStr">
+        <is>
+          <t>00400A</t>
+        </is>
+      </c>
+      <c r="B387" t="inlineStr">
+        <is>
+          <t>新增</t>
+        </is>
+      </c>
+      <c r="C387" t="inlineStr">
+        <is>
+          <t>新納入</t>
+        </is>
+      </c>
+      <c r="D387" t="inlineStr">
+        <is>
+          <t>4958</t>
+        </is>
+      </c>
+      <c r="E387" t="inlineStr"/>
+      <c r="F387" t="inlineStr">
+        <is>
+          <t>臻鼎-KY</t>
+        </is>
+      </c>
+      <c r="G387" t="inlineStr"/>
+      <c r="H387" t="inlineStr">
+        <is>
+          <t>0.46%</t>
+        </is>
+      </c>
+      <c r="I387" t="inlineStr"/>
+      <c r="J387" t="inlineStr"/>
+      <c r="K387" t="n">
+        <v>257000</v>
+      </c>
+      <c r="L387" t="inlineStr"/>
+      <c r="M387" t="inlineStr">
+        <is>
+          <t>2026-10-18_00400A_full_holdings.xlsx</t>
+        </is>
+      </c>
+    </row>
+    <row r="388">
+      <c r="A388" t="inlineStr">
+        <is>
+          <t>00400A</t>
+        </is>
+      </c>
+      <c r="B388" t="inlineStr">
+        <is>
+          <t>新增</t>
+        </is>
+      </c>
+      <c r="C388" t="inlineStr">
+        <is>
+          <t>新納入</t>
+        </is>
+      </c>
+      <c r="D388" t="inlineStr">
+        <is>
+          <t>5274</t>
+        </is>
+      </c>
+      <c r="E388" t="inlineStr"/>
+      <c r="F388" t="inlineStr">
+        <is>
+          <t>信驊</t>
+        </is>
+      </c>
+      <c r="G388" t="inlineStr"/>
+      <c r="H388" t="inlineStr">
+        <is>
+          <t>1.49%</t>
+        </is>
+      </c>
+      <c r="I388" t="inlineStr"/>
+      <c r="J388" t="inlineStr"/>
+      <c r="K388" t="n">
+        <v>28400</v>
+      </c>
+      <c r="L388" t="inlineStr"/>
+      <c r="M388" t="inlineStr">
+        <is>
+          <t>2026-10-18_00400A_full_holdings.xlsx</t>
+        </is>
+      </c>
+    </row>
+    <row r="389">
+      <c r="A389" t="inlineStr">
+        <is>
+          <t>00400A</t>
+        </is>
+      </c>
+      <c r="B389" t="inlineStr">
+        <is>
+          <t>新增</t>
+        </is>
+      </c>
+      <c r="C389" t="inlineStr">
+        <is>
+          <t>新納入</t>
+        </is>
+      </c>
+      <c r="D389" t="inlineStr">
+        <is>
+          <t>5434</t>
+        </is>
+      </c>
+      <c r="E389" t="inlineStr"/>
+      <c r="F389" t="inlineStr">
+        <is>
+          <t>崇越</t>
+        </is>
+      </c>
+      <c r="G389" t="inlineStr"/>
+      <c r="H389" t="inlineStr">
+        <is>
+          <t>0.38%</t>
+        </is>
+      </c>
+      <c r="I389" t="inlineStr"/>
+      <c r="J389" t="inlineStr"/>
+      <c r="K389" t="n">
+        <v>200000</v>
+      </c>
+      <c r="L389" t="inlineStr"/>
+      <c r="M389" t="inlineStr">
+        <is>
+          <t>2026-10-18_00400A_full_holdings.xlsx</t>
+        </is>
+      </c>
+    </row>
+    <row r="390">
+      <c r="A390" t="inlineStr">
+        <is>
+          <t>00400A</t>
+        </is>
+      </c>
+      <c r="B390" t="inlineStr">
+        <is>
+          <t>新增</t>
+        </is>
+      </c>
+      <c r="C390" t="inlineStr">
+        <is>
+          <t>新納入</t>
+        </is>
+      </c>
+      <c r="D390" t="inlineStr">
+        <is>
+          <t>6121</t>
+        </is>
+      </c>
+      <c r="E390" t="inlineStr"/>
+      <c r="F390" t="inlineStr">
+        <is>
+          <t>新普</t>
+        </is>
+      </c>
+      <c r="G390" t="inlineStr"/>
+      <c r="H390" t="inlineStr">
+        <is>
+          <t>0.21%</t>
+        </is>
+      </c>
+      <c r="I390" t="inlineStr"/>
+      <c r="J390" t="inlineStr"/>
+      <c r="K390" t="n">
+        <v>178000</v>
+      </c>
+      <c r="L390" t="inlineStr"/>
+      <c r="M390" t="inlineStr">
+        <is>
+          <t>2026-10-18_00400A_full_holdings.xlsx</t>
+        </is>
+      </c>
+    </row>
+    <row r="391">
+      <c r="A391" t="inlineStr">
+        <is>
+          <t>00400A</t>
+        </is>
+      </c>
+      <c r="B391" t="inlineStr">
+        <is>
+          <t>新增</t>
+        </is>
+      </c>
+      <c r="C391" t="inlineStr">
+        <is>
+          <t>新納入</t>
+        </is>
+      </c>
+      <c r="D391" t="inlineStr">
+        <is>
+          <t>6147</t>
+        </is>
+      </c>
+      <c r="E391" t="inlineStr"/>
+      <c r="F391" t="inlineStr">
+        <is>
+          <t>頎邦</t>
+        </is>
+      </c>
+      <c r="G391" t="inlineStr"/>
+      <c r="H391" t="inlineStr">
+        <is>
+          <t>0.88%</t>
+        </is>
+      </c>
+      <c r="I391" t="inlineStr"/>
+      <c r="J391" t="inlineStr"/>
+      <c r="K391" t="n">
+        <v>1293000</v>
+      </c>
+      <c r="L391" t="inlineStr"/>
+      <c r="M391" t="inlineStr">
+        <is>
+          <t>2026-10-18_00400A_full_holdings.xlsx</t>
+        </is>
+      </c>
+    </row>
+    <row r="392">
+      <c r="A392" t="inlineStr">
+        <is>
+          <t>00400A</t>
+        </is>
+      </c>
+      <c r="B392" t="inlineStr">
+        <is>
+          <t>新增</t>
+        </is>
+      </c>
+      <c r="C392" t="inlineStr">
+        <is>
+          <t>新納入</t>
+        </is>
+      </c>
+      <c r="D392" t="inlineStr">
+        <is>
+          <t>6187</t>
+        </is>
+      </c>
+      <c r="E392" t="inlineStr"/>
+      <c r="F392" t="inlineStr">
+        <is>
+          <t>萬潤</t>
+        </is>
+      </c>
+      <c r="G392" t="inlineStr"/>
+      <c r="H392" t="inlineStr">
+        <is>
+          <t>1.15%</t>
+        </is>
+      </c>
+      <c r="I392" t="inlineStr"/>
+      <c r="J392" t="inlineStr"/>
+      <c r="K392" t="n">
+        <v>249000</v>
+      </c>
+      <c r="L392" t="inlineStr"/>
+      <c r="M392" t="inlineStr">
+        <is>
+          <t>2026-10-18_00400A_full_holdings.xlsx</t>
+        </is>
+      </c>
+    </row>
+    <row r="393">
+      <c r="A393" t="inlineStr">
+        <is>
+          <t>00400A</t>
+        </is>
+      </c>
+      <c r="B393" t="inlineStr">
+        <is>
+          <t>新增</t>
+        </is>
+      </c>
+      <c r="C393" t="inlineStr">
+        <is>
+          <t>新納入</t>
+        </is>
+      </c>
+      <c r="D393" t="inlineStr">
+        <is>
+          <t>6271</t>
+        </is>
+      </c>
+      <c r="E393" t="inlineStr"/>
+      <c r="F393" t="inlineStr">
+        <is>
+          <t>同欣電</t>
+        </is>
+      </c>
+      <c r="G393" t="inlineStr"/>
+      <c r="H393" t="inlineStr">
+        <is>
+          <t>0.25%</t>
+        </is>
+      </c>
+      <c r="I393" t="inlineStr"/>
+      <c r="J393" t="inlineStr"/>
+      <c r="K393" t="n">
+        <v>340000</v>
+      </c>
+      <c r="L393" t="inlineStr"/>
+      <c r="M393" t="inlineStr">
+        <is>
+          <t>2026-10-18_00400A_full_holdings.xlsx</t>
+        </is>
+      </c>
+    </row>
+    <row r="394">
+      <c r="A394" t="inlineStr">
+        <is>
+          <t>00400A</t>
+        </is>
+      </c>
+      <c r="B394" t="inlineStr">
+        <is>
+          <t>新增</t>
+        </is>
+      </c>
+      <c r="C394" t="inlineStr">
+        <is>
+          <t>新納入</t>
+        </is>
+      </c>
+      <c r="D394" t="inlineStr">
+        <is>
+          <t>6278</t>
+        </is>
+      </c>
+      <c r="E394" t="inlineStr"/>
+      <c r="F394" t="inlineStr">
+        <is>
+          <t>台表科</t>
+        </is>
+      </c>
+      <c r="G394" t="inlineStr"/>
+      <c r="H394" t="inlineStr">
+        <is>
+          <t>1.74%</t>
+        </is>
+      </c>
+      <c r="I394" t="inlineStr"/>
+      <c r="J394" t="inlineStr"/>
+      <c r="K394" t="n">
+        <v>1830000</v>
+      </c>
+      <c r="L394" t="inlineStr"/>
+      <c r="M394" t="inlineStr">
+        <is>
+          <t>2026-10-18_00400A_full_holdings.xlsx</t>
+        </is>
+      </c>
+    </row>
+    <row r="395">
+      <c r="A395" t="inlineStr">
+        <is>
+          <t>00400A</t>
+        </is>
+      </c>
+      <c r="B395" t="inlineStr">
+        <is>
+          <t>新增</t>
+        </is>
+      </c>
+      <c r="C395" t="inlineStr">
+        <is>
+          <t>新納入</t>
+        </is>
+      </c>
+      <c r="D395" t="inlineStr">
+        <is>
+          <t>6669</t>
+        </is>
+      </c>
+      <c r="E395" t="inlineStr"/>
+      <c r="F395" t="inlineStr">
+        <is>
+          <t>緯穎</t>
+        </is>
+      </c>
+      <c r="G395" t="inlineStr"/>
+      <c r="H395" t="inlineStr">
+        <is>
+          <t>1.37%</t>
+        </is>
+      </c>
+      <c r="I395" t="inlineStr"/>
+      <c r="J395" t="inlineStr"/>
+      <c r="K395" t="n">
+        <v>221000</v>
+      </c>
+      <c r="L395" t="inlineStr"/>
+      <c r="M395" t="inlineStr">
+        <is>
+          <t>2026-10-18_00400A_full_holdings.xlsx</t>
+        </is>
+      </c>
+    </row>
+    <row r="396">
+      <c r="A396" t="inlineStr">
+        <is>
+          <t>00400A</t>
+        </is>
+      </c>
+      <c r="B396" t="inlineStr">
+        <is>
+          <t>新增</t>
+        </is>
+      </c>
+      <c r="C396" t="inlineStr">
+        <is>
+          <t>新納入</t>
+        </is>
+      </c>
+      <c r="D396" t="inlineStr">
+        <is>
+          <t>7750</t>
+        </is>
+      </c>
+      <c r="E396" t="inlineStr"/>
+      <c r="F396" t="inlineStr">
+        <is>
+          <t>新代</t>
+        </is>
+      </c>
+      <c r="G396" t="inlineStr"/>
+      <c r="H396" t="inlineStr">
+        <is>
+          <t>0.73%</t>
+        </is>
+      </c>
+      <c r="I396" t="inlineStr"/>
+      <c r="J396" t="inlineStr"/>
+      <c r="K396" t="n">
+        <v>122000</v>
+      </c>
+      <c r="L396" t="inlineStr"/>
+      <c r="M396" t="inlineStr">
+        <is>
+          <t>2026-10-18_00400A_full_holdings.xlsx</t>
+        </is>
+      </c>
+    </row>
+    <row r="397">
+      <c r="A397" t="inlineStr">
+        <is>
+          <t>00400A</t>
+        </is>
+      </c>
+      <c r="B397" t="inlineStr">
+        <is>
+          <t>新增</t>
+        </is>
+      </c>
+      <c r="C397" t="inlineStr">
+        <is>
+          <t>新納入</t>
+        </is>
+      </c>
+      <c r="D397" t="inlineStr">
+        <is>
+          <t>7769</t>
+        </is>
+      </c>
+      <c r="E397" t="inlineStr"/>
+      <c r="F397" t="inlineStr">
+        <is>
+          <t>鴻勁</t>
+        </is>
+      </c>
+      <c r="G397" t="inlineStr"/>
+      <c r="H397" t="inlineStr">
+        <is>
+          <t>0.12%</t>
+        </is>
+      </c>
+      <c r="I397" t="inlineStr"/>
+      <c r="J397" t="inlineStr"/>
+      <c r="K397" t="n">
+        <v>7000</v>
+      </c>
+      <c r="L397" t="inlineStr"/>
+      <c r="M397" t="inlineStr">
+        <is>
+          <t>2026-10-18_00400A_full_holdings.xlsx</t>
+        </is>
+      </c>
+    </row>
+    <row r="398">
+      <c r="A398" t="inlineStr">
+        <is>
+          <t>00400A</t>
+        </is>
+      </c>
+      <c r="B398" t="inlineStr">
+        <is>
+          <t>新增</t>
+        </is>
+      </c>
+      <c r="C398" t="inlineStr">
+        <is>
+          <t>新納入</t>
+        </is>
+      </c>
+      <c r="D398" t="inlineStr">
+        <is>
+          <t>9939</t>
+        </is>
+      </c>
+      <c r="E398" t="inlineStr"/>
+      <c r="F398" t="inlineStr">
+        <is>
+          <t>宏全</t>
+        </is>
+      </c>
+      <c r="G398" t="inlineStr"/>
+      <c r="H398" t="inlineStr">
+        <is>
+          <t>0.07%</t>
+        </is>
+      </c>
+      <c r="I398" t="inlineStr"/>
+      <c r="J398" t="inlineStr"/>
+      <c r="K398" t="n">
+        <v>180000</v>
+      </c>
+      <c r="L398" t="inlineStr"/>
+      <c r="M398" t="inlineStr">
+        <is>
+          <t>2026-10-18_00400A_full_holdings.xlsx</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
